--- a/sources/table_normalization/xlsx/environment-table44.xlsx
+++ b/sources/table_normalization/xlsx/environment-table44.xlsx
@@ -240,7 +240,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -258,7 +258,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -970,9 +969,9 @@
       <c r="A12" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
       <c r="E12" s="5">
         <f>AVERAGE(E2:E11)</f>
         <v>1.89337</v>
@@ -987,9 +986,9 @@
       <c r="A13" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
       <c r="E13" s="5">
         <f>STDEV(E2:E11)</f>
         <v>0.68796400269200098</v>
@@ -1004,9 +1003,9 @@
       <c r="A14" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
       <c r="E14" s="5">
         <f>E13/SQRT(10)</f>
         <v>0.21755331967129299</v>
@@ -1227,9 +1226,9 @@
       <c r="A26" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
       <c r="E26" s="5">
         <f>AVERAGE(E16:E25)</f>
         <v>1.5921400000000001</v>
@@ -1243,9 +1242,9 @@
       <c r="A27" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
       <c r="E27" s="5">
         <f>STDEV(E16:E25)</f>
         <v>0.66567387110105702</v>
@@ -1259,9 +1258,9 @@
       <c r="A28" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
       <c r="E28" s="5">
         <f>E27/SQRT(10)</f>
         <v>0.21050456115406799</v>
@@ -1461,9 +1460,9 @@
       <c r="A39" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
       <c r="E39" s="5">
         <f>AVERAGE(E30:E38)</f>
         <v>1.26573333333333</v>
@@ -1477,9 +1476,9 @@
       <c r="A40" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
       <c r="E40" s="5">
         <f>STDEV(E30:E38)</f>
         <v>0.31969075291600202</v>
@@ -1493,9 +1492,9 @@
       <c r="A41" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
       <c r="E41" s="5">
         <f>E40/SQRT(9)</f>
         <v>0.106563584305334</v>
@@ -1695,9 +1694,9 @@
       <c r="A52" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B52" s="6"/>
-      <c r="C52" s="6"/>
-      <c r="D52" s="6"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
       <c r="E52" s="5">
         <f>AVERAGE(E43:E51)</f>
         <v>1.03467777777778</v>
@@ -1711,9 +1710,9 @@
       <c r="A53" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
       <c r="E53" s="5">
         <f>STDEV(E43:E51)</f>
         <v>0.51827775318302505</v>
@@ -1727,9 +1726,9 @@
       <c r="A54" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
       <c r="E54" s="5">
         <f>E53/SQRT(9)</f>
         <v>0.17275925106100801</v>
@@ -1829,9 +1828,9 @@
       <c r="A60" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B60" s="6"/>
-      <c r="C60" s="6"/>
-      <c r="D60" s="6"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
       <c r="E60" s="5">
         <f>AVERAGE(E56:E59)</f>
         <v>0.49280000000000002</v>
@@ -1845,9 +1844,9 @@
       <c r="A61" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
       <c r="E61" s="5">
         <f>STDEV(E56:E59)</f>
         <v>6.9102098376243204E-2</v>
@@ -1861,9 +1860,9 @@
       <c r="A62" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B62" s="6"/>
-      <c r="C62" s="6"/>
-      <c r="D62" s="6"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
       <c r="E62" s="5">
         <f>E61/SQRT(4)</f>
         <v>3.4551049188121602E-2</v>
@@ -1963,9 +1962,6 @@
       <c r="A68" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B68" s="7"/>
-      <c r="C68" s="7"/>
-      <c r="D68" s="7"/>
       <c r="E68" s="5">
         <f>AVERAGE(E64:E67)</f>
         <v>0.45982499999999998</v>
@@ -1979,9 +1975,6 @@
       <c r="A69" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B69" s="7"/>
-      <c r="C69" s="7"/>
-      <c r="D69" s="7"/>
       <c r="E69" s="5">
         <f>STDEV(E64:E67)</f>
         <v>0.143752156505563</v>
@@ -1995,9 +1988,6 @@
       <c r="A70" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B70" s="7"/>
-      <c r="C70" s="7"/>
-      <c r="D70" s="7"/>
       <c r="E70" s="5">
         <f>E69/SQRT(4)</f>
         <v>7.1876078252781694E-2</v>
